--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486362_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486362_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2362</v>
+        <v>6.7652</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3162</v>
+        <v>3.9376</v>
       </c>
       <c r="F2" t="n">
-        <v>2.92</v>
+        <v>2.8276</v>
       </c>
       <c r="G2" t="n">
         <v>1.6263</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9574</v>
+        <v>0.4864</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8857</v>
+        <v>0.5071</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0717</v>
+        <v>-0.0207</v>
       </c>
       <c r="V2" t="n">
         <v>2.2599</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6638</v>
+        <v>6.5938</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8336</v>
+        <v>6.4861</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1697</v>
+        <v>0.1077</v>
       </c>
       <c r="G3" t="n">
         <v>5.522</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9457</v>
+        <v>-1.0157</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0154</v>
+        <v>-0.3629</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9302</v>
+        <v>-0.6528</v>
       </c>
       <c r="V3" t="n">
         <v>0.5649999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>A. BARCELLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3414</v>
+        <v>3.8775</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2121</v>
+        <v>5.0901</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1293</v>
+        <v>-1.2126</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4044</v>
+        <v>3.7977</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0459</v>
+        <v>3.5523</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3586</v>
+        <v>0.2454</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6587</v>
+        <v>4.5908</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4292</v>
+        <v>3.6895</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2295</v>
+        <v>0.9013</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2543</v>
+        <v>-0.7931</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3834</v>
+        <v>-0.1372</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1291</v>
+        <v>-0.6558</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9147</v>
+        <v>-0.7027</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2281</v>
+        <v>-0.1081</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6865</v>
+        <v>-0.5946</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9347</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3252</v>
+        <v>1.695</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BARCELLO</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5132</v>
+        <v>3.428</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0649</v>
+        <v>1.1342</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5516</v>
+        <v>2.2938</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7977</v>
+        <v>1.0594</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5523</v>
+        <v>3.23</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2454</v>
+        <v>-2.1706</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5908</v>
+        <v>0.6682</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6895</v>
+        <v>2.1383</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9013</v>
+        <v>-1.4702</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7931</v>
+        <v>0.3912</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1372</v>
+        <v>1.0916</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6558</v>
+        <v>-0.7004</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>2.3926</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.067</v>
+        <v>-0.0664</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1334</v>
+        <v>0.2283</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9336</v>
+        <v>-0.2947</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>1.695</v>
+        <v>1.3252</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5781</v>
+        <v>2.9233</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4384</v>
+        <v>2.318</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1397</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0594</v>
+        <v>0.4044</v>
       </c>
       <c r="H6" t="n">
-        <v>3.23</v>
+        <v>0.0459</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1706</v>
+        <v>0.3586</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6682</v>
+        <v>0.6587</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1383</v>
+        <v>0.4292</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4702</v>
+        <v>0.2295</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3912</v>
+        <v>-0.2543</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0916</v>
+        <v>-0.3834</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7004</v>
+        <v>0.1291</v>
       </c>
       <c r="P6" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3926</v>
+        <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9163</v>
+        <v>0.4966</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4675</v>
+        <v>0.3341</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4488</v>
+        <v>0.1625</v>
       </c>
       <c r="V6" t="n">
-        <v>1.13</v>
+        <v>0.9347</v>
       </c>
       <c r="W6" t="n">
         <v>1.3252</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1952</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4449</v>
+        <v>2.2612</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8428</v>
+        <v>0.9366</v>
       </c>
       <c r="F7" t="n">
-        <v>1.602</v>
+        <v>1.3246</v>
       </c>
       <c r="G7" t="n">
         <v>0.537</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5805</v>
+        <v>0.3969</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2704</v>
+        <v>-0.1766</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8509</v>
+        <v>0.5735</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1952</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3676</v>
+        <v>1.7771</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2793</v>
+        <v>1.5654</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0883</v>
+        <v>0.2116</v>
       </c>
       <c r="G8" t="n">
         <v>2.0438</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3237</v>
+        <v>-0.2668</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2846</v>
+        <v>0.5708</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9609</v>
+        <v>-0.8376</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2994</v>
+        <v>1.6407</v>
       </c>
       <c r="E9" t="n">
-        <v>1.127</v>
+        <v>1.3758</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1724</v>
+        <v>0.2649</v>
       </c>
       <c r="G9" t="n">
         <v>0.191</v>
@@ -1156,13 +1156,13 @@
         <v>2.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1318</v>
+        <v>0.2094</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1334</v>
+        <v>0.1154</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0016</v>
+        <v>0.094</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9347</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7639</v>
+        <v>1.187</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3502</v>
+        <v>0.1653</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1141</v>
+        <v>1.0217</v>
       </c>
       <c r="G10" t="n">
         <v>0.755</v>
@@ -1234,13 +1234,13 @@
         <v>3.0451</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8187</v>
+        <v>-0.3957</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9589</v>
+        <v>-0.4434</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1402</v>
+        <v>0.0478</v>
       </c>
       <c r="V10" t="n">
         <v>-1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5384</v>
+        <v>-0.3341</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8015</v>
+        <v>-0.6898</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2632</v>
+        <v>0.3556</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8295</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0737</v>
+        <v>0.2779</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0565</v>
+        <v>0.0553</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1301</v>
+        <v>0.2226</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3945</v>
+        <v>-0.8914</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5832000000000001</v>
+        <v>1.0555</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9777</v>
+        <v>-1.9469</v>
       </c>
       <c r="G12" t="n">
         <v>3.2138</v>
@@ -1390,13 +1390,13 @@
         <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9781</v>
+        <v>-0.475</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1935</v>
+        <v>0.2788</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7846</v>
+        <v>-0.7538</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8902</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6067</v>
+        <v>-2.1893</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9823</v>
+        <v>-1.4416</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6244</v>
+        <v>-0.7477</v>
       </c>
       <c r="G13" t="n">
         <v>-3.5585</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0928</v>
+        <v>-0.6754</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8784</v>
+        <v>-0.3377</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2144</v>
+        <v>-0.3377</v>
       </c>
       <c r="V13" t="n">
         <v>0.7395</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.6689</v>
+        <v>27.039</v>
       </c>
       <c r="E14" t="n">
-        <v>20.5635</v>
+        <v>21.9332</v>
       </c>
       <c r="F14" t="n">
-        <v>5.105600000000001</v>
+        <v>5.1056</v>
       </c>
       <c r="G14" t="n">
         <v>14.7624</v>
@@ -1516,7 +1516,7 @@
         <v>20.3005</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.5381</v>
+        <v>-5.538099999999999</v>
       </c>
       <c r="J14" t="n">
         <v>19.1066</v>
@@ -1531,7 +1531,7 @@
         <v>-4.3442</v>
       </c>
       <c r="N14" t="n">
-        <v>6.2621</v>
+        <v>6.262099999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-10.6063</v>
@@ -1546,13 +1546,13 @@
         <v>18.4879</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.1004</v>
+        <v>-1.7305</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7090000000000001</v>
+        <v>0.6610999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.391499999999999</v>
+        <v>-2.3915</v>
       </c>
       <c r="V14" t="n">
         <v>2.044</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1099</v>
+        <v>4.2917</v>
       </c>
       <c r="E15" t="n">
-        <v>7.6095</v>
+        <v>6.8272</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4996</v>
+        <v>-2.5355</v>
       </c>
       <c r="G15" t="n">
         <v>0.4881</v>
@@ -1624,13 +1624,13 @@
         <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9268</v>
+        <v>1.1086</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6992</v>
+        <v>0.9169</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2276</v>
+        <v>0.1917</v>
       </c>
       <c r="V15" t="n">
         <v>2.2599</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2406</v>
+        <v>0.8817</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2432</v>
+        <v>0.8358</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0026</v>
+        <v>0.0459</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0216</v>
+        <v>0.0339</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0303</v>
+        <v>-0.9064</v>
       </c>
       <c r="I16" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.9403</v>
       </c>
       <c r="J16" t="n">
-        <v>1.236</v>
+        <v>0.7997</v>
       </c>
       <c r="K16" t="n">
-        <v>1.083</v>
+        <v>0.073</v>
       </c>
       <c r="L16" t="n">
-        <v>0.153</v>
+        <v>0.7267</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2576</v>
+        <v>-0.7659</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1134</v>
+        <v>-0.9794</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1443</v>
+        <v>0.2136</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1767</v>
+        <v>0.1953</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1392</v>
+        <v>0.0361</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0375</v>
+        <v>0.1592</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3473</v>
+        <v>-0.2584</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3888</v>
+        <v>0.2373</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0415</v>
+        <v>-0.4958</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0339</v>
+        <v>-0.0216</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9064</v>
+        <v>-0.0303</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9403</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7997</v>
+        <v>1.236</v>
       </c>
       <c r="K17" t="n">
-        <v>0.073</v>
+        <v>1.083</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7267</v>
+        <v>0.153</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7659</v>
+        <v>-1.2576</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9794</v>
+        <v>-1.1134</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2136</v>
+        <v>-0.1443</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6525</v>
+        <v>-1.305</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3391</v>
+        <v>0.6778</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.411</v>
+        <v>0.1334</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.5444</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3301</v>
+        <v>-0.4705</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4868</v>
+        <v>0.6137</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8169</v>
+        <v>-1.0843</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1164</v>
+        <v>1.9319</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1857</v>
+        <v>-0.0092</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3021</v>
+        <v>1.9411</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6132</v>
+        <v>1.9392</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3454</v>
+        <v>0.6387</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2677</v>
+        <v>1.3005</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.7296</v>
+        <v>-0.0073</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1598</v>
+        <v>-0.6479</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5698</v>
+        <v>0.6407</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4801</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1805</v>
+        <v>0.2055</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5729</v>
+        <v>-0.2379</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3924</v>
+        <v>0.4434</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7809</v>
+        <v>-1.5204</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7809</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7943</v>
+        <v>-1.3308</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1667</v>
+        <v>1.0339</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.961</v>
+        <v>-2.3648</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9319</v>
+        <v>-1.1164</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0092</v>
+        <v>0.1857</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9411</v>
+        <v>-1.3021</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9392</v>
+        <v>2.6132</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6387</v>
+        <v>2.3454</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3005</v>
+        <v>0.2677</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0073</v>
+        <v>-3.7296</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6479</v>
+        <v>-2.1598</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6407</v>
+        <v>-1.5698</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>-3.4801</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1183</v>
+        <v>1.1798</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6850000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5667</v>
+        <v>0.0598</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5204</v>
+        <v>0.7809</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.7809</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4642</v>
+        <v>-2.5099</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7809</v>
+        <v>-1.2222</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6833</v>
+        <v>-1.2877</v>
       </c>
       <c r="G20" t="n">
         <v>-3.7741</v>
@@ -2014,13 +2014,13 @@
         <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.428</v>
+        <v>0.5264</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4074</v>
+        <v>0.1514</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0207</v>
+        <v>0.3749</v>
       </c>
       <c r="V20" t="n">
         <v>0.9554</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>T. NASPLER PERAIRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6577</v>
+        <v>-3.2426</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8236</v>
+        <v>-1.6059</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8341</v>
+        <v>-1.6367</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9799</v>
+        <v>0.4985</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3783</v>
+        <v>-0.8912</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6016</v>
+        <v>1.3897</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4162</v>
+        <v>2.0701</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.7696</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2677</v>
+        <v>1.3005</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5637</v>
+        <v>-1.5716</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6943</v>
+        <v>-1.6608</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8694</v>
+        <v>0.0892</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-3.6976</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6475</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6802</v>
+        <v>0.0216</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0327</v>
+        <v>0.0649</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3252</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3252</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. NASPLER PERAIRE</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7127</v>
+        <v>-3.4213</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8294</v>
+        <v>-0.8236</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8833</v>
+        <v>-2.5977</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4985</v>
+        <v>-2.9799</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8912</v>
+        <v>-2.3783</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3897</v>
+        <v>-0.6016</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0701</v>
+        <v>-0.4162</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7696</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3005</v>
+        <v>0.2677</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5716</v>
+        <v>-2.5637</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6608</v>
+        <v>-1.6943</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0892</v>
+        <v>-0.8694</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.6976</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3836</v>
+        <v>0.8839</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2019</v>
+        <v>0.6802</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1817</v>
+        <v>0.2037</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3974</v>
+        <v>-3.6896</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1247</v>
+        <v>-2.5659</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2727</v>
+        <v>-1.1237</v>
       </c>
       <c r="G23" t="n">
         <v>-3.9162</v>
@@ -2248,13 +2248,13 @@
         <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5034999999999999</v>
+        <v>0.2043</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.274</v>
+        <v>0.2848</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2295</v>
+        <v>-0.0805</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1952</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.5356</v>
+        <v>-5.946</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.8754</v>
+        <v>-4.3166</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6601</v>
+        <v>-1.6293</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6741</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8615</v>
+        <v>-0.2719</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3014</v>
+        <v>-0.7426</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4399</v>
+        <v>0.4708</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.4747</v>
+        <v>-8.4831</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.6965</v>
+        <v>-5.2494</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.7783</v>
+        <v>-3.2337</v>
       </c>
       <c r="G25" t="n">
         <v>-2.2325</v>
@@ -2404,13 +2404,13 @@
         <v>0.435</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1971</v>
+        <v>-0.2055</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4194</v>
+        <v>0.0277</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.2331</v>
       </c>
       <c r="V25" t="n">
         <v>-1.695</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-25.6689</v>
+        <v>-24.1788</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.235499999999999</v>
+        <v>-6.2357</v>
       </c>
       <c r="F26" t="n">
-        <v>-19.4334</v>
+        <v>-17.9433</v>
       </c>
       <c r="G26" t="n">
         <v>-14.7624</v>
@@ -2455,7 +2455,7 @@
         <v>5.5381</v>
       </c>
       <c r="J26" t="n">
-        <v>4.344300000000001</v>
+        <v>4.3443</v>
       </c>
       <c r="K26" t="n">
         <v>-6.2622</v>
@@ -2470,7 +2470,7 @@
         <v>-14.0384</v>
       </c>
       <c r="O26" t="n">
-        <v>-5.0684</v>
+        <v>-5.068399999999999</v>
       </c>
       <c r="P26" t="n">
         <v>-11.9628</v>
@@ -2479,16 +2479,16 @@
         <v>-18.4879</v>
       </c>
       <c r="R26" t="n">
-        <v>6.525</v>
+        <v>6.524999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1004</v>
+        <v>4.5907</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3914</v>
+        <v>2.3916</v>
       </c>
       <c r="U26" t="n">
-        <v>0.7089</v>
+        <v>2.1992</v>
       </c>
       <c r="V26" t="n">
         <v>-2.0442</v>
